--- a/especificacion/EDT_Fundacion_Chile_Maria_Pinto_KPI.xlsx
+++ b/especificacion/EDT_Fundacion_Chile_Maria_Pinto_KPI.xlsx
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="H3" s="70" t="n">
-        <v>1800</v>
+        <v>1369</v>
       </c>
       <c r="I3" s="58" t="str"/>
       <c r="J3" s="58" t="inlineStr">
@@ -14683,7 +14683,7 @@
         </is>
       </c>
       <c r="L3" s="70" t="n">
-        <v>50</v>
+        <v>38.0278</v>
       </c>
       <c r="M3" s="69" t="n">
         <v>46245</v>
@@ -14730,7 +14730,7 @@
         </is>
       </c>
       <c r="H4" s="70" t="n">
-        <v>1500</v>
+        <v>1054.48</v>
       </c>
       <c r="I4" s="58" t="str"/>
       <c r="J4" s="58" t="inlineStr">
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="L4" s="70" t="n">
-        <v>41.6667</v>
+        <v>29.2911</v>
       </c>
       <c r="M4" s="69" t="n">
         <v>46245</v>
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="H5" s="70" t="n">
-        <v>1500</v>
+        <v>1904.68</v>
       </c>
       <c r="I5" s="58" t="str"/>
       <c r="J5" s="58" t="inlineStr">
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="L5" s="70" t="n">
-        <v>41.6667</v>
+        <v>52.9078</v>
       </c>
       <c r="M5" s="69" t="n">
         <v>46245</v>
@@ -14913,7 +14913,7 @@
         </is>
       </c>
       <c r="H7" s="70" t="n">
-        <v>1800</v>
+        <v>1369</v>
       </c>
       <c r="I7" s="58" t="str"/>
       <c r="J7" s="58" t="inlineStr">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="L7" s="70" t="n">
-        <v>50</v>
+        <v>38.0278</v>
       </c>
       <c r="M7" s="69" t="n">
         <v>46245</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="H8" s="70" t="n">
-        <v>1500</v>
+        <v>1054.48</v>
       </c>
       <c r="I8" s="58" t="str"/>
       <c r="J8" s="58" t="inlineStr">
@@ -14988,7 +14988,7 @@
         </is>
       </c>
       <c r="L8" s="70" t="n">
-        <v>41.6667</v>
+        <v>29.2911</v>
       </c>
       <c r="M8" s="69" t="n">
         <v>46245</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="H9" s="70" t="n">
-        <v>1500</v>
+        <v>1904.68</v>
       </c>
       <c r="I9" s="58" t="str"/>
       <c r="J9" s="58" t="inlineStr">
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="L9" s="70" t="n">
-        <v>41.6667</v>
+        <v>52.9078</v>
       </c>
       <c r="M9" s="69" t="n">
         <v>46245</v>
